--- a/output/pdf_financials_xlsx/TGII.xlsx
+++ b/output/pdf_financials_xlsx/TGII.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.0694</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.077056</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.146544</v>
       </c>
     </row>
     <row r="93">
@@ -3111,7 +3111,11 @@
           <t>Share-based payment reserve (note 12)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.07340000000000001</v>
       </c>
@@ -3134,7 +3138,11 @@
           <t>Warrant reserve (note 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.996</v>
       </c>

--- a/output/pdf_financials_xlsx/TGII.xlsx
+++ b/output/pdf_financials_xlsx/TGII.xlsx
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.039785</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.08724</v>
       </c>
     </row>
     <row r="68">
